--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.45412872886554</v>
+        <v>3.648795918440651</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19649291296943</v>
+        <v>3.444430098357532</v>
       </c>
       <c r="E2" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F2" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.49606348136336</v>
+        <v>4.305610315721546</v>
       </c>
       <c r="D3" t="n">
-        <v>26.23127753715629</v>
+        <v>4.262582599787897</v>
       </c>
       <c r="E3" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F3" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.11390815403559</v>
+        <v>4.081010075030783</v>
       </c>
       <c r="D4" t="n">
-        <v>24.21374560552221</v>
+        <v>3.93473366089736</v>
       </c>
       <c r="E4" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F4" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.99389964738693</v>
+        <v>3.574008692700376</v>
       </c>
       <c r="D5" t="n">
-        <v>21.98893788708995</v>
+        <v>3.573202406652116</v>
       </c>
       <c r="E5" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F5" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.8809031123286</v>
+        <v>6.318146755753397</v>
       </c>
       <c r="D6" t="n">
-        <v>29.01361258676985</v>
+        <v>4.7147120453501</v>
       </c>
       <c r="E6" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F6" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.75046621623583</v>
+        <v>9.871950760138322</v>
       </c>
       <c r="D7" t="n">
-        <v>60.81744033920578</v>
+        <v>9.88283405512094</v>
       </c>
       <c r="E7" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F7" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.62753885532886</v>
+        <v>11.47697506399094</v>
       </c>
       <c r="D8" t="n">
-        <v>70.68336447410637</v>
+        <v>11.48604672704229</v>
       </c>
       <c r="E8" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F8" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>55.16308745795997</v>
+        <v>8.964001711918495</v>
       </c>
       <c r="D9" t="n">
-        <v>55.0959537216954</v>
+        <v>8.953092479775503</v>
       </c>
       <c r="E9" t="n">
-        <v>18.15060283349155</v>
+        <v>2.949472960442378</v>
       </c>
       <c r="F9" t="n">
-        <v>18.79397179782639</v>
+        <v>3.054020417146789</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
